--- a/daily/2026-03-31.xlsx
+++ b/daily/2026-03-31.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -710,7 +728,6 @@
       <c r="V3" t="n">
         <v>21</v>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
         <v>-11.8</v>
       </c>
@@ -788,7 +805,6 @@
       <c r="V4" t="n">
         <v>21</v>
       </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
         <v>5.4</v>
       </c>
@@ -1030,7 +1046,6 @@
       <c r="V7" t="n">
         <v>29</v>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
         <v>-7.9</v>
       </c>
@@ -1190,7 +1205,6 @@
       <c r="V9" t="n">
         <v>21</v>
       </c>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
         <v>2</v>
       </c>
@@ -1268,7 +1282,6 @@
       <c r="V10" t="n">
         <v>21</v>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
         <v>3.3</v>
       </c>
@@ -1510,7 +1523,6 @@
       <c r="V13" t="n">
         <v>29</v>
       </c>
-      <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
         <v>-7.9</v>
       </c>
@@ -1588,7 +1600,6 @@
       <c r="V14" t="n">
         <v>30</v>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
         <v>8.6</v>
       </c>
@@ -1666,7 +1677,6 @@
       <c r="V15" t="n">
         <v>18</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
         <v>10.3</v>
       </c>
@@ -1744,7 +1754,6 @@
       <c r="V16" t="n">
         <v>18</v>
       </c>
-      <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
         <v>6</v>
       </c>
@@ -1822,7 +1831,6 @@
       <c r="V17" t="n">
         <v>30</v>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="n">
         <v>-4.2</v>
       </c>
@@ -2146,7 +2154,6 @@
       <c r="V21" t="n">
         <v>30</v>
       </c>
-      <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
         <v>16.9</v>
       </c>
@@ -2634,7 +2641,6 @@
       <c r="V27" t="n">
         <v>14</v>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
         <v>-11.5</v>
       </c>
@@ -2712,7 +2718,6 @@
       <c r="V28" t="n">
         <v>2</v>
       </c>
-      <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
         <v>-10.4</v>
       </c>
@@ -2790,7 +2795,6 @@
       <c r="V29" t="n">
         <v>14</v>
       </c>
-      <c r="W29" t="inlineStr"/>
       <c r="X29" t="n">
         <v>13.4</v>
       </c>
@@ -3114,7 +3118,6 @@
       <c r="V33" t="n">
         <v>2</v>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="n">
         <v>-18.1</v>
       </c>
@@ -3684,7 +3687,6 @@
       <c r="V40" t="n">
         <v>17</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>8.199999999999999</v>
       </c>
@@ -4172,7 +4174,6 @@
       <c r="V46" t="n">
         <v>25</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>-10</v>
       </c>
@@ -4332,7 +4333,6 @@
       <c r="V48" t="n">
         <v>22</v>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="n">
         <v>4.1</v>
       </c>
@@ -4492,7 +4492,6 @@
       <c r="V50" t="n">
         <v>27</v>
       </c>
-      <c r="W50" t="inlineStr"/>
       <c r="X50" t="n">
         <v>7.1</v>
       </c>
@@ -4556,7 +4555,7 @@
         <v>1.7</v>
       </c>
       <c r="R51" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>4.4</v>
@@ -4570,7 +4569,6 @@
       <c r="V51" t="n">
         <v>22</v>
       </c>
-      <c r="W51" t="inlineStr"/>
       <c r="X51" t="n">
         <v>-5.8</v>
       </c>
@@ -5044,7 +5042,7 @@
         <v>-0.3</v>
       </c>
       <c r="R57" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>-4.6</v>
@@ -5132,7 +5130,7 @@
         <v>6.7</v>
       </c>
       <c r="T58" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
         <v>2</v>
@@ -5140,7 +5138,6 @@
       <c r="V58" t="n">
         <v>27</v>
       </c>
-      <c r="W58" t="inlineStr"/>
       <c r="X58" t="n">
         <v>12.8</v>
       </c>
@@ -5218,7 +5215,6 @@
       <c r="V59" t="n">
         <v>27</v>
       </c>
-      <c r="W59" t="inlineStr"/>
       <c r="X59" t="n">
         <v>-13.1</v>
       </c>
@@ -5378,7 +5374,6 @@
       <c r="V61" t="n">
         <v>19</v>
       </c>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="n">
         <v>20.3</v>
       </c>
@@ -5702,7 +5697,6 @@
       <c r="V65" t="n">
         <v>19</v>
       </c>
-      <c r="W65" t="inlineStr"/>
       <c r="X65" t="n">
         <v>10.4</v>
       </c>
@@ -5780,7 +5774,6 @@
       <c r="V66" t="n">
         <v>10</v>
       </c>
-      <c r="W66" t="inlineStr"/>
       <c r="X66" t="n">
         <v>39.2</v>
       </c>
@@ -5858,7 +5851,6 @@
       <c r="V67" t="n">
         <v>10</v>
       </c>
-      <c r="W67" t="inlineStr"/>
       <c r="X67" t="n">
         <v>2</v>
       </c>
@@ -6100,7 +6092,6 @@
       <c r="V70" t="n">
         <v>10</v>
       </c>
-      <c r="W70" t="inlineStr"/>
       <c r="X70" t="n">
         <v>11.1</v>
       </c>
@@ -6260,7 +6251,6 @@
       <c r="V72" t="n">
         <v>10</v>
       </c>
-      <c r="W72" t="inlineStr"/>
       <c r="X72" t="n">
         <v>4</v>
       </c>
@@ -6502,7 +6492,6 @@
       <c r="V75" t="n">
         <v>26</v>
       </c>
-      <c r="W75" t="inlineStr"/>
       <c r="X75" t="n">
         <v>-24.5</v>
       </c>
@@ -6580,7 +6569,6 @@
       <c r="V76" t="n">
         <v>26</v>
       </c>
-      <c r="W76" t="inlineStr"/>
       <c r="X76" t="n">
         <v>-7</v>
       </c>
@@ -6740,7 +6728,6 @@
       <c r="V78" t="n">
         <v>26</v>
       </c>
-      <c r="W78" t="inlineStr"/>
       <c r="X78" t="n">
         <v>9.4</v>
       </c>
@@ -6818,7 +6805,6 @@
       <c r="V79" t="n">
         <v>20</v>
       </c>
-      <c r="W79" t="inlineStr"/>
       <c r="X79" t="n">
         <v>2.6</v>
       </c>
@@ -7142,7 +7128,6 @@
       <c r="V83" t="n">
         <v>20</v>
       </c>
-      <c r="W83" t="inlineStr"/>
       <c r="X83" t="n">
         <v>-0.9</v>
       </c>
@@ -11359,1663 +11344,3509 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>PHX @ ORL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Silva scored 9 pts vs 10.5 line (-1.5), UNDER hit by 1.5 pts. Silva played 25 min (-5.1 vs L10 avg of 30.2) — 17% less than expected. Shooting efficiency was cold: 27.3% FG (-19.2% vs L10 avg of 46.5%). 3/11 from the field. Signals that called it correctly: Context, Defense, H2H, Pace (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.7 pts — actual 9 was 2.3 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Silva's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>PHX @ ORL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Banchero scored 19 pts vs 22.5 line (-3.5), OVER missed by 3.5 pts. Minutes were as expected: 37 played vs L10 avg 35.6. Shooting was in line with averages: 42.9% FG (6/14, L10 avg 40.6%). Counter-signals that proved correct: HR L10, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 26.8 pts — actual 19 was 7.8 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Banchero's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PHX @ ORL</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 15 pts vs 10.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 28 played vs L10 avg 30.8. Shooting was in line with averages: 57.1% FG (4/7, L10 avg 54.5%). Counter-signals that proved correct: Volume, HR L10, Trend, Defense. Signals that were wrong: HR L30, Context, Pace. Projection model targeted 7.7 pts — actual 15 was 7.3 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Jr.'s recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>PHX @ ORL</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Bane scored 21 pts vs 19.5 line (+1.5), OVER hit by 1.5 pts. Bane played 37 min (+3.6 vs L10 avg of 33.7) — 11% more than expected. Shooting efficiency was cold: 37.5% FG (-9.2% vs L10 avg of 46.7%). 6/16 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 24.1 pts — actual 21 was 3.1 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Bane's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Jalen Green</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>PHX @ ORL</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Green scored 8 pts vs 21.5 line (-13.5), UNDER hit by 13.5 pts. Green played 20 min (-10.7 vs L10 avg of 30.4) — 35% less than expected. Shooting efficiency was cold: 30.0% FG (-16.7% vs L10 avg of 46.7%). 3/10 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, FG Trend. Projection model targeted 17.7 pts — actual 8 was 9.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Green's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Collin Gillespie</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>PHX @ ORL</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E7" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Gillespie scored 11 pts vs 12.5 line (-1.5), OVER missed by 1.5 pts. Minutes were as expected: 27 played vs L10 avg 29.0. Shooting efficiency was hot: 50.0% FG (+19.5% vs L10 avg of 30.5%). 4/8 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, H2H. Signals that were wrong: Volume, Context, Defense. Projection model targeted 13.6 pts — actual 11 was 2.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Dillon Brooks</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>PHX @ ORL</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E8" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Brooks scored 9 pts vs 13.5 line (-4.5), UNDER hit by 4.5 pts. Brooks played 22 min (-7.2 vs L10 avg of 29.0) — 25% less than expected. Shooting efficiency was cold: 30.8% FG (-13.7% vs L10 avg of 44.5%). 4/13 from the field. Signals that called it correctly: H2H, Pace, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.4 pts — actual 9 was 3.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Brooks's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>PHX @ ORL</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Suggs scored 20 pts vs 13.5 line (+6.5), OVER hit by 6.5 pts. Suggs played 38 min (+7.6 vs L10 avg of 30.1) — 25% more than expected. Shooting efficiency was hot: 54.5% FG (+7.9% vs L10 avg of 46.6%). 6/11 from the field. Signals that called it correctly: Context, FG Trend, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 15.2 pts — actual 20 was 4.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Suggs's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Jevon Carter</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>PHX @ ORL</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Carter scored 0 pts vs 6.5 line (-6.5), OVER missed by 6.5 pts. Minutes were as expected: 22 played vs L10 avg 20.4. Shooting efficiency was cold: 0.0% FG (-45.0% vs L10 avg of 45.0%). 0/6 from the field. Counter-signals that proved correct: HR L30, Defense, H2H, Pace. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 15.0 pts — actual 0 was 15.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Grayson Allen</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>PHX @ ORL</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Allen scored 10 pts vs 14.5 line (-4.5), OVER missed by 4.5 pts. Allen played 32 min (+5.9 vs L10 avg of 26.3) — 22% more than expected. Shooting efficiency was cold: 28.6% FG (-10.1% vs L10 avg of 38.7%). 4/14 from the field. Counter-signals that proved correct: Trend, Pace, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 20.0 pts — actual 10 was 10.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Oso Ighodaro</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>PHX @ ORL</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Ighodaro scored 5 pts vs 9.5 line (-4.5), OVER missed by 4.5 pts. Ighodaro played 24 min (-6.0 vs L10 avg of 30.5) — 20% less than expected. Shooting efficiency was hot: 100.0% FG (+32.9% vs L10 avg of 67.1%). 2/2 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Defense. Signals that were wrong: HR L10, Trend, Min Trend. Projection model targeted 12.0 pts — actual 5 was 7.0 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Ighodaro for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Devin Booker</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>PHX @ ORL</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E13" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Booker scored 34 pts vs 26.5 line (+7.5), UNDER missed by 7.5 pts. Booker played 36 min (+3.2 vs L10 avg of 32.9) — 10% more than expected. Shooting was in line with averages: 50.0% FG (8/16, L10 avg 48.0%). Counter-signals that proved correct: HR L30, HR L10, Defense, H2H. Signals that were wrong: Volume, Trend, Context. Projection model targeted 20.0 pts — actual 34 was 14.0 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Booker's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>CHA @ BKN</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E14" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Miller scored 25 pts vs 20.5 line (+4.5), OVER hit by 4.5 pts. Minutes were as expected: 29 played vs L10 avg 31.3. Shooting efficiency was hot: 53.8% FG (+9.7% vs L10 avg of 44.1%). 7/13 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, Min Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 24.0 pts — actual 25 was 1.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Miller in this role.</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Drake Powell</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>CHA @ BKN</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E15" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Powell scored 10 pts vs 8.5 line (+1.5), UNDER missed by 1.5 pts. Powell played 28 min (+3.0 vs L10 avg of 25.3) — 12% more than expected. Shooting efficiency was cold: 33.3% FG (-8.2% vs L10 avg of 41.5%). 3/9 from the field. Counter-signals that proved correct: HR L10, Trend, H2H, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 7.6 pts — actual 10 was 2.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Nolan Traore</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>CHA @ BKN</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Traore scored 10 pts vs 11.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 23 played vs L10 avg 22.1. Shooting efficiency was hot: 50.0% FG (+20.3% vs L10 avg of 29.7%). 4/8 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, H2H. Projection model targeted 5.9 pts — actual 10 was 4.1 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Kon Knueppel</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>CHA @ BKN</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Knueppel scored 8 pts vs 18.5 line (-10.5), UNDER hit by 10.5 pts. Knueppel played 25 min (-5.1 vs L10 avg of 29.8) — 17% less than expected. Shooting efficiency was cold: 33.3% FG (-11.1% vs L10 avg of 44.4%). 4/12 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, Pace (7/10 aligned). Counter-signals that were wrong: Volume, Defense, H2H. Projection model targeted 14.5 pts — actual 8 was 6.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Knueppel's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Coby White</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>CHA @ BKN</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>WIN — White scored 16 pts vs 14.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 21 played vs L10 avg 20.8. Shooting was in line with averages: 41.7% FG (5/12, L10 avg 46.6%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Pace, Min Trend. Projection model targeted 20.0 pts — actual 16 was 4.0 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Noah Clowney</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>CHA @ BKN</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Clowney scored 4 pts vs 10.5 line (-6.5), UNDER hit by 6.5 pts. Minutes were as expected: 20 played vs L10 avg 22.1. Shooting efficiency was cold: 16.7% FG (-20.1% vs L10 avg of 36.8%). 1/6 from the field. Signals that called it correctly: HR L10, Trend, Defense, H2H, Pace (7/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 5.8 pts — actual 4 was 1.8 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Clowney in this role.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Miles Bridges</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>CHA @ BKN</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Bridges scored 19 pts vs 14.5 line (+4.5), UNDER missed by 4.5 pts. Bridges played 24 min (-5.7 vs L10 avg of 29.4) — 19% less than expected. Shooting efficiency was hot: 58.3% FG (+7.2% vs L10 avg of 51.1%). 7/12 from the field. Counter-signals that proved correct: Defense, H2H, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.3 pts — actual 19 was 6.7 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Bridges for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Grant Williams</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>CHA @ BKN</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Williams scored 10 pts vs 5.5 line (+4.5), OVER hit by 4.5 pts. Minutes were as expected: 20 played vs L10 avg 18.6. Shooting efficiency was hot: 57.1% FG (+15.7% vs L10 avg of 41.4%). 4/7 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 8.7 pts — actual 10 was 1.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Williams in this role.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Ziaire Williams</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>CHA @ BKN</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Williams scored 10 pts vs 12.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 24 played vs L10 avg 23.2. Shooting efficiency was cold: 40.0% FG (-10.1% vs L10 avg of 50.1%). 4/10 from the field. Signals that called it correctly: Volume, Context, Defense, H2H, Pace (6/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 12.0 pts — actual 10 was 2.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Williams in this role.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>CHA @ BKN</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Diabaté scored 10 pts vs 8.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 27 played vs L10 avg 27.8. Shooting efficiency was hot: 66.7% FG (+9.1% vs L10 avg of 57.6%). 4/6 from the field. Signals that called it correctly: Trend, Context, Defense, H2H (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.6 pts — actual 10 was 1.6 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Diabaté in this role.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>LaMelo Ball</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>CHA @ BKN</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E24" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Ball scored 14 pts vs 20.5 line (-6.5), UNDER hit by 6.5 pts. Minutes were as expected: 28 played vs L10 avg 27.9. Shooting efficiency was cold: 33.3% FG (-10.5% vs L10 avg of 43.8%). 4/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (7/10 aligned). Counter-signals that were wrong: Trend, Defense, FG Trend. Projection model targeted 12.9 pts — actual 14 was 1.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Ball in this role.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Ousmane Dieng</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>DAL @ MIL</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E25" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Dieng scored 11 pts vs 13.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 29 played vs L10 avg 28.1. Shooting was in line with averages: 40.0% FG (4/10, L10 avg 40.4%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 7.9 pts — actual 11 was 3.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Dieng's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Max Christie</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>DAL @ MIL</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Christie scored 3 pts vs 11.5 line (-8.5), UNDER hit by 8.5 pts. Minutes were as expected: 26 played vs L10 avg 28.4. Shooting efficiency was cold: 8.3% FG (-39.3% vs L10 avg of 47.6%). 1/12 from the field. Signals that called it correctly: Trend, Context, H2H, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.0 pts — actual 3 was 7.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Christie's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>P.J. Washington</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>DAL @ MIL</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="5" t="n">
         <v>14.5</v>
       </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Ryan Rollins</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>DAL @ MIL</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Rollins scored 24 pts vs 20.5 line (+3.5), UNDER missed by 3.5 pts. Rollins played 36 min (+4.1 vs L10 avg of 31.5) — 13% more than expected. Shooting was in line with averages: 57.1% FG (8/14, L10 avg 52.6%). Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.8 pts — actual 24 was 7.2 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Rollins's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Cooper Flagg</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>DAL @ MIL</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E29" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Flagg scored 19 pts vs 20.5 line (-1.5), OVER missed by 1.5 pts. Minutes were as expected: 32 played vs L10 avg 34.5. Shooting efficiency was cold: 31.6% FG (-15.3% vs L10 avg of 46.9%). 6/19 from the field. Counter-signals that proved correct: HR L30, H2H. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 22.0 pts — actual 19 was 3.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Kyle Kuzma</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>DAL @ MIL</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E30" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Kuzma scored 20 pts vs 12.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 23 played vs L10 avg 25.2. Shooting was in line with averages: 52.9% FG (9/17, L10 avg 53.8%). Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 11.6 pts — actual 20 was 8.4 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Kuzma's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Dwight Powell</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>DAL @ MIL</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="E31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Powell scored 3 pts vs 4.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 15 played vs L10 avg 12.2. Shooting efficiency was hot: 100.0% FG (+70.3% vs L10 avg of 29.7%). 1/1 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (7/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 3.7 pts — actual 3 was 0.7 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Powell in this role.</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Myles Turner</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>DAL @ MIL</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E32" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Turner scored 10 pts vs 11.5 line (-1.5), OVER missed by 1.5 pts. Turner played 27 min (+3.7 vs L10 avg of 23.6) — 16% more than expected. Shooting was in line with averages: 37.5% FG (3/8, L10 avg 41.2%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, H2H. Projection model targeted 12.7 pts — actual 10 was 2.7 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Taurean Prince</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>DAL @ MIL</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Prince scored 6 pts vs 9.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 22 played vs L10 avg 22.4. Shooting efficiency was cold: 20.0% FG (-19.0% vs L10 avg of 39.0%). 2/10 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, FG Trend (6/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 5.5 pts — actual 6 was 0.5 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Prince in this role.</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Naji Marshall</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>DAL @ MIL</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="5" t="n">
         <v>16.5</v>
       </c>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Jakob Poeltl</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>TOR @ DET</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Poeltl scored 13 pts vs 10.5 line (+2.5), UNDER missed by 2.5 pts. Poeltl played 24 min (-3.1 vs L10 avg of 26.6) — 12% less than expected. Shooting was in line with averages: 66.7% FG (6/9, L10 avg 63.1%). Counter-signals that proved correct: Volume, HR L10, Trend, H2H. Signals that were wrong: HR L30, Context, Defense. Projection model targeted 10.6 pts — actual 13 was 2.4 pts off (wrong direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Poeltl's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Duncan Robinson</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>TOR @ DET</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E36" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Robinson scored 19 pts vs 11.5 line (+7.5), UNDER missed by 7.5 pts. Robinson played 29 min (+3.5 vs L10 avg of 25.5) — 14% more than expected. Shooting efficiency was hot: 66.7% FG (+15.4% vs L10 avg of 51.3%). 6/9 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, H2H. Projection model targeted 8.4 pts — actual 19 was 10.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Ausar Thompson</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>TOR @ DET</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E37" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Thompson scored 5 pts vs 9.5 line (-4.5), UNDER hit by 4.5 pts. Minutes were as expected: 26 played vs L10 avg 25.4. Shooting efficiency was cold: 33.3% FG (-13.7% vs L10 avg of 47.0%). 2/6 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (9/10 aligned). Counter-signals that were wrong: Trend. Projection model targeted 4.8 pts — actual 5 was 0.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Tobias Harris</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>TOR @ DET</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Harris scored 12 pts vs 13.5 line (-1.5), UNDER hit by 1.5 pts. Harris played 33 min (+5.7 vs L10 avg of 27.2) — 21% more than expected. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 48.0%). Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 12.9 pts — actual 12 was 0.9 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Harris in this role.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Scottie Barnes</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>TOR @ DET</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E39" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Barnes scored 5 pts vs 17.5 line (-12.5), UNDER hit by 12.5 pts. Barnes played 28 min (-4.0 vs L10 avg of 31.7) — 13% less than expected. Shooting efficiency was cold: 25.0% FG (-31.4% vs L10 avg of 56.4%). 2/8 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (7/10 aligned). Counter-signals that were wrong: Trend, H2H, FG Trend. Projection model targeted 16.5 pts — actual 5 was 11.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Barnes's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Brandon Ingram</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>TOR @ DET</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E40" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Ingram scored 22 pts vs 20.5 line (+1.5), UNDER missed by 1.5 pts. Ingram played 31 min (-3.3 vs L10 avg of 34.1) — 10% less than expected. Shooting was in line with averages: 46.7% FG (7/15, L10 avg 47.0%). Counter-signals that proved correct: Volume, H2H. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 20.2 pts — actual 22 was 1.8 pts close (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Sandro Mamukelashvili</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>TOR @ DET</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Mamukelashvili scored 16 pts vs 8.5 line (+7.5), OVER hit by 7.5 pts. Minutes were as expected: 22 played vs L10 avg 19.6. Shooting was in line with averages: 53.8% FG (7/13, L10 avg 57.1%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, Min Trend. Projection model targeted 11.2 pts — actual 16 was 4.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Mamukelashvili's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Kevin Huerter</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>TOR @ DET</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Huerter scored 8 pts vs 9.5 line (-1.5), OVER missed by 1.5 pts. Minutes were as expected: 22 played vs L10 avg 24.3. Shooting efficiency was cold: 33.3% FG (-11.8% vs L10 avg of 45.1%). 2/6 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Defense. Signals that were wrong: HR L10, Trend, H2H. Projection model targeted 9.7 pts — actual 8 was 1.7 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Jamal Shead</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>TOR @ DET</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E43" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Shead scored 6 pts vs 7.5 line (-1.5), UNDER hit by 1.5 pts. Shead played 29 min (+5.5 vs L10 avg of 23.8) — 23% more than expected. Shooting was in line with averages: 28.6% FG (2/7, L10 avg 30.0%). Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, Min Trend. Projection model targeted 4.4 pts — actual 6 was 1.6 pts close (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Ja'Kobe Walter</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>TOR @ DET</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Walter scored 3 pts vs 10.5 line (-7.5), UNDER hit by 7.5 pts. Walter played 27 min (+4.4 vs L10 avg of 22.3) — 20% more than expected. Shooting efficiency was cold: 16.7% FG (-36.7% vs L10 avg of 53.4%). 1/6 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 8.5 pts — actual 3 was 5.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Walter's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Jalen Duren</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>TOR @ DET</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E45" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Duren scored 31 pts vs 20.5 line (+10.5), OVER hit by 10.5 pts. Duren played 35 min (+5.4 vs L10 avg of 29.2) — 18% more than expected. Shooting efficiency was hot: 92.3% FG (+22.5% vs L10 avg of 69.8%). 12/13 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 21.3 pts — actual 31 was 9.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Duren's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Daniss Jenkins</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>TOR @ DET</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E46" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jenkins scored 21 pts vs 14.5 line (+6.5), UNDER missed by 6.5 pts. Jenkins played 37 min (+5.1 vs L10 avg of 31.5) — 16% more than expected. Shooting efficiency was hot: 55.6% FG (+11.4% vs L10 avg of 44.2%). 5/9 from the field. Counter-signals that proved correct: HR L10, Trend, H2H, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 10.4 pts — actual 21 was 10.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>RJ Barrett</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>TOR @ DET</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E47" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Barrett scored 24 pts vs 20.5 line (+3.5), UNDER missed by 3.5 pts. Minutes were as expected: 31 played vs L10 avg 30.1. Shooting efficiency was hot: 58.3% FG (+5.8% vs L10 avg of 52.5%). 7/12 from the field. Counter-signals that proved correct: HR L10, Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 16.2 pts — actual 24 was 7.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>OG Anunoby</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>NYK @ HOU</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E48" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Anunoby scored 8 pts vs 15.5 line (-7.5), OVER missed by 7.5 pts. Anunoby played 38 min (+4.6 vs L10 avg of 33.6) — 14% more than expected. Shooting efficiency was cold: 33.3% FG (-19.0% vs L10 avg of 52.3%). 3/9 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 20.0 pts — actual 8 was 12.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Karl-Anthony Towns</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>NYK @ HOU</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E49" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Towns scored 22 pts vs 16.5 line (+5.5), OVER hit by 5.5 pts. Towns played 34 min (+4.4 vs L10 avg of 29.8) — 15% more than expected. Shooting efficiency was cold: 41.2% FG (-15.2% vs L10 avg of 56.4%). 7/17 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Defense, Pace. Projection model targeted 19.3 pts — actual 22 was 2.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Jabari Smith Jr.</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>NYK @ HOU</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E50" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 15 pts vs 14.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 39 played vs L10 avg 37.1. Shooting efficiency was hot: 50.0% FG (+7.5% vs L10 avg of 42.5%). 5/10 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Min Trend (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 16.1 pts — actual 15 was 1.1 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Jr. in this role.</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Mitchell Robinson</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>NYK @ HOU</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="E51" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Robinson scored 5 pts vs 4.5 line (+0.5), OVER hit by 0.5 pts. Robinson played 16 min (-5.3 vs L10 avg of 21.2) — 25% less than expected. Shooting efficiency was cold: 50.0% FG (-26.5% vs L10 avg of 76.5%). 2/4 from the field. Signals that called it correctly: Volume, HR L30, Context, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 6.5 pts — actual 5 was 1.5 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Robinson in this role.</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Jalen Brunson</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>NYK @ HOU</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E52" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Brunson scored 12 pts vs 24.5 line (-12.5), OVER missed by 12.5 pts. Minutes were as expected: 37 played vs L10 avg 37.1. Shooting efficiency was cold: 35.7% FG (-11.5% vs L10 avg of 47.2%). 5/14 from the field. Counter-signals that proved correct: Volume, Defense, Pace. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 27.4 pts — actual 12 was 15.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Josh Hart</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>NYK @ HOU</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E53" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Hart scored 13 pts vs 12.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 28 played vs L10 avg 30.5. Shooting efficiency was cold: 41.7% FG (-16.2% vs L10 avg of 57.9%). 5/12 from the field. Counter-signals that proved correct: HR L10, Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 9.8 pts — actual 13 was 3.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Tari Eason</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>NYK @ HOU</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E54" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Eason scored 17 pts vs 7.5 line (+9.5), UNDER missed by 9.5 pts. Eason played 30 min (+6.7 vs L10 avg of 23.7) — 28% more than expected. Shooting efficiency was hot: 60.0% FG (+29.9% vs L10 avg of 30.1%). 6/10 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 7.0 pts — actual 17 was 10.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Amen Thompson</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>NYK @ HOU</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E55" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Thompson scored 17 pts vs 15.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 39 played vs L10 avg 38.4. Shooting was in line with averages: 57.1% FG (8/14, L10 avg 54.5%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Defense, Pace. Projection model targeted 16.1 pts — actual 17 was 0.9 pts close (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Jose Alvarado</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>NYK @ HOU</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E56" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Alvarado scored 12 pts vs 6.5 line (+5.5), UNDER missed by 5.5 pts. Minutes were as expected: 12 played vs L10 avg 13.8. Shooting efficiency was hot: 83.3% FG (+55.7% vs L10 avg of 27.6%). 5/6 from the field. Counter-signals that proved correct: H2H. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.6 pts — actual 12 was 6.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Mikal Bridges</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>NYK @ HOU</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E57" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Bridges scored 7 pts vs 13.5 line (-6.5), UNDER hit by 6.5 pts. Bridges played 34 min (+3.1 vs L10 avg of 30.6) — 10% more than expected. Shooting efficiency was hot: 75.0% FG (+33.9% vs L10 avg of 41.1%). 3/4 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, H2H. Projection model targeted 11.6 pts — actual 7 was 4.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Alperen Sengun</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>NYK @ HOU</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E58" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Sengun scored 13 pts vs 19.5 line (-6.5), OVER missed by 6.5 pts. Minutes were as expected: 30 played vs L10 avg 32.8. Shooting efficiency was hot: 80.0% FG (+20.3% vs L10 avg of 59.7%). 4/5 from the field. Counter-signals that proved correct: HR L30, HR L10, Defense, H2H. Signals that were wrong: Volume, Trend, Context. Projection model targeted 20.4 pts — actual 13 was 7.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Kevin Durant</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>NYK @ HOU</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="3" t="n">
         <v>25.5</v>
       </c>
+      <c r="E59" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Durant scored 27 pts vs 25.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 34 played vs L10 avg 35.5. Shooting was in line with averages: 55.6% FG (10/18, L10 avg 55.0%). Signals that called it correctly: Trend, Context, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 26.0 pts — actual 27 was 1.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Durant in this role.</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Reed Sheppard</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>NYK @ HOU</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E60" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Sheppard scored 20 pts vs 13.5 line (+6.5), UNDER missed by 6.5 pts. Minutes were as expected: 28 played vs L10 avg 29.2. Shooting efficiency was hot: 66.7% FG (+26.9% vs L10 avg of 39.8%). 8/12 from the field. Counter-signals that proved correct: Volume, HR L30, Min Trend. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 8.7 pts — actual 20 was 11.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Max Strus</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="5" t="n">
         <v>10.5</v>
       </c>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="inlineStr"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>James Harden</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="5" t="n">
         <v>20.5</v>
       </c>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="inlineStr"/>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>Jarrett Allen</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="5" t="n">
         <v>11.5</v>
       </c>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="inlineStr"/>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>LeBron James</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="5" t="n">
         <v>18.5</v>
       </c>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="5" t="inlineStr"/>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>Evan Mobley</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="5" t="n">
         <v>17.5</v>
       </c>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="inlineStr"/>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Deandre Ayton</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="5" t="n">
         <v>10.5</v>
       </c>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="inlineStr"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>Austin Reaves</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="5" t="n">
         <v>22.5</v>
       </c>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="5" t="inlineStr"/>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>Donovan Mitchell</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="5" t="n">
         <v>25.5</v>
       </c>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="inlineStr"/>
+      <c r="I68" s="5" t="n"/>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>Sam Merrill</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="5" t="n">
         <v>12.5</v>
       </c>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="5" t="inlineStr"/>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>Jaxson Hayes</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="5" t="n">
         <v>6.5</v>
       </c>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="inlineStr"/>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>Rui Hachimura</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="5" t="n">
         <v>9.5</v>
       </c>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="inlineStr"/>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>Luka Dončić</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="5" t="n">
         <v>31.5</v>
       </c>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="inlineStr"/>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Brook Lopez</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="5" t="n">
         <v>10.5</v>
       </c>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="5" t="inlineStr"/>
+      <c r="I73" s="5" t="n"/>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>Toumani Camara</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="5" t="n">
         <v>13.5</v>
       </c>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="inlineStr"/>
+      <c r="I74" s="5" t="n"/>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>Robert Williams III</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="5" t="n">
         <v>6.5</v>
       </c>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="5" t="inlineStr"/>
+      <c r="I75" s="5" t="n"/>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>Jrue Holiday</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="5" t="n">
         <v>16.5</v>
       </c>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="5" t="inlineStr"/>
+      <c r="I76" s="5" t="n"/>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>Donovan Clingan</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="5" t="n">
         <v>13.5</v>
       </c>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="5" t="inlineStr"/>
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>Scoot Henderson</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="5" t="n">
         <v>17.5</v>
       </c>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="5" t="inlineStr"/>
+      <c r="I78" s="5" t="n"/>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>Bennedict Mathurin</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="5" t="n">
         <v>18.5</v>
       </c>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="5" t="inlineStr"/>
+      <c r="I79" s="5" t="n"/>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>Darius Garland</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="5" t="n">
         <v>19.5</v>
       </c>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="inlineStr"/>
+      <c r="I80" s="5" t="n"/>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>John Collins</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="5" t="n">
         <v>12.5</v>
       </c>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="5" t="inlineStr"/>
+      <c r="I81" s="5" t="n"/>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>Deni Avdija</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="5" t="n">
         <v>25.5</v>
       </c>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="5" t="inlineStr"/>
+      <c r="I82" s="5" t="n"/>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>Kawhi Leonard</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="5" t="n">
         <v>28.5</v>
       </c>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="5" t="inlineStr"/>
+      <c r="I83" s="5" t="n"/>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>Derrick Jones Jr.</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="5" t="n">
         <v>9.5</v>
+      </c>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="5" t="inlineStr"/>
+      <c r="I84" s="5" t="n"/>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:00</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/daily/2026-03-31.xlsx
+++ b/daily/2026-03-31.xlsx
@@ -12523,7 +12523,7 @@
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-01 06:00</t>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
@@ -12833,7 +12833,7 @@
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>2026-04-01 06:00</t>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
@@ -14034,274 +14034,370 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Max Strus</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D61" s="5" t="n">
+      <c r="D61" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E61" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Strus scored 11 pts vs 10.5 line (+0.5), OVER hit by 0.5 pts. Strus played 23 min (-3.3 vs L10 avg of 26.5) — 12% less than expected. Shooting efficiency was hot: 50.0% FG (+6.1% vs L10 avg of 43.9%). 4/8 from the field. Signals that called it correctly: Volume, Context, Min Trend (3/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 16.3 pts — actual 11 was 5.3 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Strus's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>James Harden</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D62" s="5" t="n">
+      <c r="D62" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="n"/>
-      <c r="H62" s="5" t="inlineStr"/>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E62" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Harden scored 17 pts vs 20.5 line (-3.5), UNDER hit by 3.5 pts. Harden played 28 min (-8.2 vs L10 avg of 35.9) — 23% less than expected. Shooting was in line with averages: 46.2% FG (6/13, L10 avg 48.8%). Signals that called it correctly: HR L30, HR L10, Trend, Defense, H2H (6/10 aligned). Counter-signals that were wrong: Volume, Context, FG Trend. Projection model targeted 19.0 pts — actual 17 was 2.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Harden in this role.</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Jarrett Allen</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D63" s="5" t="n">
+      <c r="D63" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="n"/>
-      <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E63" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Allen scored 18 pts vs 11.5 line (+6.5), OVER hit by 6.5 pts. Allen played 19 min (-8.9 vs L10 avg of 27.5) — 32% less than expected. Shooting efficiency was hot: 81.8% FG (+8.3% vs L10 avg of 73.5%). 9/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, Min Trend. Projection model targeted 23.4 pts — actual 18 was 5.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Allen's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>LeBron James</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D64" s="5" t="n">
+      <c r="D64" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="inlineStr"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E64" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>WIN — James scored 14 pts vs 18.5 line (-4.5), UNDER hit by 4.5 pts. James played 31 min (-5.0 vs L10 avg of 35.6) — 14% less than expected. Shooting was in line with averages: 50.0% FG (4/8, L10 avg 54.8%). Signals that called it correctly: HR L10, Trend (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 16.3 pts — actual 14 was 2.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms James's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Evan Mobley</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D65" s="5" t="n">
+      <c r="D65" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="n"/>
-      <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E65" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Mobley scored 6 pts vs 17.5 line (-11.5), OVER missed by 11.5 pts. Mobley played 22 min (-9.7 vs L10 avg of 31.2) — 31% less than expected. Shooting efficiency was cold: 50.0% FG (-17.4% vs L10 avg of 67.4%). 2/4 from the field. Counter-signals that proved correct: Defense, H2H, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 24.9 pts — actual 6 was 18.9 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Mobley for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Deandre Ayton</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D66" s="5" t="n">
+      <c r="D66" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="n"/>
-      <c r="H66" s="5" t="inlineStr"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E66" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Ayton scored 18 pts vs 10.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 28 played vs L10 avg 28.8. Shooting efficiency was cold: 61.5% FG (-14.0% vs L10 avg of 75.5%). 8/13 from the field. Counter-signals that proved correct: Volume, HR L10, Defense, H2H. Signals that were wrong: HR L30, Trend, Context. Projection model targeted 7.7 pts — actual 18 was 10.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Austin Reaves</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D67" s="5" t="n">
+      <c r="D67" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E67" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Reaves scored 19 pts vs 22.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 37 played vs L10 avg 38.9. Shooting efficiency was cold: 37.5% FG (-9.2% vs L10 avg of 46.7%). 6/16 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 17.5 pts — actual 19 was 1.5 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Reaves in this role.</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Donovan Mitchell</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D68" s="5" t="n">
+      <c r="D68" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="5" t="inlineStr"/>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E68" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Mitchell scored 10 pts vs 25.5 line (-15.5), OVER missed by 15.5 pts. Mitchell played 24 min (-10.1 vs L10 avg of 34.3) — 29% less than expected. Shooting was in line with averages: 40.0% FG (4/10, L10 avg 43.6%). Counter-signals that proved correct: HR L30, HR L10, Defense, H2H. Signals that were wrong: Volume, Trend, Context. Projection model targeted 25.7 pts — actual 10 was 15.7 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Mitchell for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
@@ -14335,517 +14431,697 @@
       <c r="I69" s="5" t="n"/>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>2026-04-01 06:00</t>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>Jaxson Hayes</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D70" s="5" t="n">
+      <c r="D70" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="inlineStr"/>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E70" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Hayes scored 4 pts vs 6.5 line (-2.5), OVER missed by 2.5 pts. Minutes were as expected: 19 played vs L10 avg 20.5. Shooting was in line with averages: 50.0% FG (2/4, L10 avg 53.2%). Counter-signals that proved correct: HR L10, H2H, FG Trend. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 9.3 pts — actual 4 was 5.3 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Hayes's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>Rui Hachimura</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D71" s="5" t="n">
+      <c r="D71" s="4" t="n">
         <v>9.5</v>
       </c>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="inlineStr"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E71" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Hachimura scored 14 pts vs 9.5 line (+4.5), UNDER missed by 4.5 pts. Hachimura played 19 min (-6.6 vs L10 avg of 25.5) — 26% less than expected. Shooting efficiency was hot: 75.0% FG (+21.0% vs L10 avg of 54.0%). 6/8 from the field. Counter-signals that proved correct: Volume, HR L30, Defense, Pace. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 2.4 pts — actual 14 was 11.6 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Hachimura for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>Luka Dončić</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>CLE @ LAL</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D72" s="5" t="n">
+      <c r="D72" s="4" t="n">
         <v>31.5</v>
       </c>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="5" t="inlineStr"/>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E72" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Dončić scored 42 pts vs 31.5 line (+10.5), UNDER missed by 10.5 pts. Dončić played 34 min (-4.4 vs L10 avg of 38.4) — 11% less than expected. Shooting was in line with averages: 50.0% FG (13/26, L10 avg 48.7%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: none. Projection model targeted 30.9 pts — actual 42 was 11.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Dončić for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>Brook Lopez</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D73" s="5" t="n">
+      <c r="D73" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="5" t="inlineStr"/>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E73" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Lopez scored 18 pts vs 10.5 line (+7.5), OVER hit by 7.5 pts. Lopez played 36 min (+8.0 vs L10 avg of 27.8) — 29% more than expected. Shooting was in line with averages: 43.8% FG (7/16, L10 avg 46.3%). Signals that called it correctly: Trend, Context, Defense, H2H, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.1 pts — actual 18 was 5.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Lopez's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Toumani Camara</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D74" s="5" t="n">
+      <c r="D74" s="4" t="n">
         <v>13.5</v>
       </c>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="n"/>
-      <c r="H74" s="5" t="inlineStr"/>
-      <c r="I74" s="5" t="n"/>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E74" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Camara scored 17 pts vs 13.5 line (+3.5), UNDER missed by 3.5 pts. Minutes were as expected: 33 played vs L10 avg 29.9. Shooting efficiency was cold: 43.8% FG (-6.8% vs L10 avg of 50.6%). 7/16 from the field. Counter-signals that proved correct: HR L10, Trend, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 9.3 pts — actual 17 was 7.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Robert Williams III</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D75" s="5" t="n">
+      <c r="D75" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="5" t="inlineStr"/>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E75" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>WIN — III scored 6 pts vs 6.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 18 played vs L10 avg 18.0. Shooting efficiency was hot: 100.0% FG (+40.4% vs L10 avg of 59.6%). 3/3 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, Defense (7/10 aligned). Counter-signals that were wrong: Volume, H2H, Min Trend. Projection model targeted 3.2 pts — actual 6 was 2.8 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms III's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Jrue Holiday</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D76" s="5" t="n">
+      <c r="D76" s="4" t="n">
         <v>16.5</v>
       </c>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="n"/>
-      <c r="H76" s="5" t="inlineStr"/>
-      <c r="I76" s="5" t="n"/>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E76" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Holiday scored 30 pts vs 16.5 line (+13.5), UNDER missed by 13.5 pts. Holiday played 32 min (+3.2 vs L10 avg of 28.6) — 11% more than expected. Shooting efficiency was hot: 47.6% FG (+5.4% vs L10 avg of 42.2%). 10/21 from the field. Counter-signals that proved correct: Defense, H2H, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.7 pts — actual 30 was 16.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Donovan Clingan</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D77" s="5" t="n">
+      <c r="D77" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="5" t="inlineStr"/>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E77" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Clingan scored 4 pts vs 13.5 line (-9.5), UNDER hit by 9.5 pts. Minutes were as expected: 29 played vs L10 avg 26.9. Shooting efficiency was cold: 40.0% FG (-10.8% vs L10 avg of 50.8%). 2/5 from the field. Signals that called it correctly: Trend, Context, Defense, H2H, Pace (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.4 pts — actual 4 was 8.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Clingan's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Scoot Henderson</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D78" s="5" t="n">
+      <c r="D78" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="E78" s="5" t="n"/>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="n"/>
-      <c r="H78" s="5" t="inlineStr"/>
-      <c r="I78" s="5" t="n"/>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E78" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Henderson scored 15 pts vs 17.5 line (-2.5), UNDER hit by 2.5 pts. Henderson played 29 min (+4.2 vs L10 avg of 24.6) — 17% more than expected. Shooting efficiency was cold: 35.7% FG (-7.7% vs L10 avg of 43.4%). 5/14 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Pace (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 16.6 pts — actual 15 was 1.6 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Henderson in this role.</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Bennedict Mathurin</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D79" s="5" t="n">
+      <c r="D79" s="4" t="n">
         <v>18.5</v>
       </c>
-      <c r="E79" s="5" t="n"/>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="n"/>
-      <c r="H79" s="5" t="inlineStr"/>
-      <c r="I79" s="5" t="n"/>
-      <c r="J79" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E79" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Mathurin scored 4 pts vs 18.5 line (-14.5), OVER missed by 14.5 pts. Mathurin played 22 min (-7.4 vs L10 avg of 29.8) — 25% less than expected. Shooting efficiency was cold: 28.6% FG (-16.0% vs L10 avg of 44.6%). 2/7 from the field. Counter-signals that proved correct: HR L30, H2H, Pace, Min Trend. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 20.0 pts — actual 4 was 16.0 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Mathurin for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>Darius Garland</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D80" s="5" t="n">
+      <c r="D80" s="4" t="n">
         <v>19.5</v>
       </c>
-      <c r="E80" s="5" t="n"/>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="n"/>
-      <c r="H80" s="5" t="inlineStr"/>
-      <c r="I80" s="5" t="n"/>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E80" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Garland scored 20 pts vs 19.5 line (+0.5), UNDER missed by 0.5 pts. Garland played 37 min (+8.0 vs L10 avg of 29.2) — 27% more than expected. Shooting efficiency was cold: 41.2% FG (-13.0% vs L10 avg of 54.2%). 7/17 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: H2H, Pace, Min Trend. Projection model targeted 17.6 pts — actual 20 was 2.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>John Collins</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D81" s="5" t="n">
+      <c r="D81" s="4" t="n">
         <v>12.5</v>
       </c>
-      <c r="E81" s="5" t="n"/>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="n"/>
-      <c r="H81" s="5" t="inlineStr"/>
-      <c r="I81" s="5" t="n"/>
-      <c r="J81" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E81" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Collins scored 17 pts vs 12.5 line (+4.5), UNDER missed by 4.5 pts. Collins played 31 min (+6.7 vs L10 avg of 24.5) — 27% more than expected. Shooting efficiency was hot: 87.5% FG (+43.7% vs L10 avg of 43.8%). 7/8 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Defense. Signals that were wrong: HR L10, Trend, Pace. Projection model targeted 11.0 pts — actual 17 was 6.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>Deni Avdija</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D82" s="5" t="n">
+      <c r="D82" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="n"/>
-      <c r="H82" s="5" t="inlineStr"/>
-      <c r="I82" s="5" t="n"/>
-      <c r="J82" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E82" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Avdija scored 28 pts vs 25.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 34 played vs L10 avg 31.6. Shooting efficiency was hot: 53.3% FG (+7.1% vs L10 avg of 46.2%). 8/15 from the field. Counter-signals that proved correct: FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 21.9 pts — actual 28 was 6.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>Kawhi Leonard</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D83" s="5" t="n">
+      <c r="D83" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="E83" s="5" t="n"/>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="n"/>
-      <c r="H83" s="5" t="inlineStr"/>
-      <c r="I83" s="5" t="n"/>
-      <c r="J83" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E83" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Leonard scored 23 pts vs 28.5 line (-5.5), OVER missed by 5.5 pts. Leonard played 36 min (+5.2 vs L10 avg of 30.3) — 17% more than expected. Shooting efficiency was cold: 46.7% FG (-7.5% vs L10 avg of 54.2%). 7/15 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, FG Trend. Projection model targeted 30.7 pts — actual 23 was 7.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Derrick Jones Jr.</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>POR @ LAC</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D84" s="5" t="n">
+      <c r="D84" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="n"/>
-      <c r="H84" s="5" t="inlineStr"/>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:00</t>
+      <c r="E84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 1 pts vs 9.5 line (-8.5), UNDER hit by 8.5 pts. Jr. played 23 min (-5.9 vs L10 avg of 29.3) — 20% less than expected. Shooting efficiency was cold: 0.0% FG (-48.0% vs L10 avg of 48.0%). 0/2 from the field. Signals that called it correctly: Trend, Pace, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.9 pts — actual 1 was 7.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:07</t>
         </is>
       </c>
     </row>
